--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/23,09,26 Останкино СЫРЫ/дв 23,09,26 млрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/23,09,26 Останкино СЫРЫ/дв 23,09,26 млрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\23,09,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881A30D3-EDAE-4265-8833-0E4CBF225C38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD780E51-0407-4BA2-856B-F4D1FCF37E6E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>шт</t>
-  </si>
-  <si>
-    <t>17,09,26 - нет на заводе / 10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 30,07,26 - нет на заводе</t>
   </si>
   <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
@@ -383,6 +380,9 @@
   </si>
   <si>
     <t>28,09,</t>
+  </si>
+  <si>
+    <t>24,09,26 - нет на заводе / 17,09,26 - нет на заводе / 10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 30,07,26 - нет на заводе</t>
   </si>
 </sst>
 </file>
@@ -2720,13 +2720,13 @@
         <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="T3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>17</v>
@@ -2812,7 +2812,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>3463</v>
+        <v>3415</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
@@ -3076,7 +3076,7 @@
         <v>4.1176000000000004</v>
       </c>
       <c r="AG6" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AH6" s="1">
         <f>G6*R6</f>
@@ -3140,8 +3140,7 @@
         <v>24</v>
       </c>
       <c r="S7" s="5">
-        <f>VLOOKUP(A7,заказ!A:B,2,0)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T7" s="16">
         <f>VLOOKUP(A7,[1]Sheet!$A:$R,18,0)</f>
@@ -3186,7 +3185,7 @@
         <v>6.4</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AH7" s="1">
         <f t="shared" ref="AH7:AH51" si="6">G7*R7</f>
@@ -3212,7 +3211,7 @@
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>37</v>
@@ -3252,8 +3251,7 @@
         <v>24</v>
       </c>
       <c r="S8" s="5">
-        <f>VLOOKUP(A8,заказ!A:B,2,0)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T8" s="16">
         <f>VLOOKUP(A8,[1]Sheet!$A:$R,18,0)</f>
@@ -3298,7 +3296,7 @@
         <v>7.8</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AH8" s="1">
         <f t="shared" si="6"/>
@@ -3324,7 +3322,7 @@
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -3438,7 +3436,7 @@
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>37</v>
@@ -3520,7 +3518,7 @@
         <v>0.2</v>
       </c>
       <c r="AG10" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH10" s="1">
         <f t="shared" si="6"/>
@@ -3546,7 +3544,7 @@
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
@@ -3630,7 +3628,7 @@
         <v>32.4</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH11" s="1">
         <f t="shared" si="6"/>
@@ -3656,7 +3654,7 @@
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>37</v>
@@ -3744,7 +3742,7 @@
         <v>17.399999999999999</v>
       </c>
       <c r="AG12" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AH12" s="1">
         <f t="shared" si="6"/>
@@ -3770,7 +3768,7 @@
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>37</v>
@@ -3887,7 +3885,7 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>37</v>
@@ -3975,7 +3973,7 @@
         <v>29.8</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AH14" s="1">
         <f t="shared" si="6"/>
@@ -4001,7 +3999,7 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>37</v>
@@ -4084,7 +4082,7 @@
         <v>1.8</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" si="6"/>
@@ -4110,7 +4108,7 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -4224,7 +4222,7 @@
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
@@ -4338,7 +4336,7 @@
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>37</v>
@@ -4419,7 +4417,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="AG18" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH18" s="1">
         <f t="shared" si="6"/>
@@ -4445,7 +4443,7 @@
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>37</v>
@@ -4530,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="AG19" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AH19" s="1">
         <f t="shared" si="6"/>
@@ -4556,7 +4554,7 @@
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -4672,7 +4670,7 @@
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>37</v>
@@ -4789,7 +4787,7 @@
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>37</v>
@@ -4872,7 +4870,7 @@
         <v>1.6</v>
       </c>
       <c r="AG22" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH22" s="1">
         <f t="shared" si="6"/>
@@ -4898,7 +4896,7 @@
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>37</v>
@@ -5013,7 +5011,7 @@
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>37</v>
@@ -5097,7 +5095,7 @@
         <v>1.8</v>
       </c>
       <c r="AG24" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH24" s="1">
         <f t="shared" si="6"/>
@@ -5123,7 +5121,7 @@
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>37</v>
@@ -5206,7 +5204,7 @@
         <v>0.8</v>
       </c>
       <c r="AG25" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH25" s="1">
         <f t="shared" si="6"/>
@@ -5232,7 +5230,7 @@
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -5314,7 +5312,7 @@
         <v>0.65100000000000002</v>
       </c>
       <c r="AG26" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH26" s="1">
         <f t="shared" si="6"/>
@@ -5340,7 +5338,7 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>35</v>
@@ -5415,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="AG27" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AH27" s="1">
         <f t="shared" si="6"/>
@@ -5441,7 +5439,7 @@
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>37</v>
@@ -5550,7 +5548,7 @@
     </row>
     <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>37</v>
@@ -5633,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="AG29" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AH29" s="1">
         <f t="shared" si="6"/>
@@ -5659,7 +5657,7 @@
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>37</v>
@@ -5771,7 +5769,7 @@
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>37</v>
@@ -5883,7 +5881,7 @@
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>37</v>
@@ -5962,7 +5960,7 @@
         <v>35</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AH32" s="1">
         <f t="shared" si="6"/>
@@ -5988,7 +5986,7 @@
     </row>
     <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>37</v>
@@ -6105,7 +6103,7 @@
     </row>
     <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>37</v>
@@ -6214,7 +6212,7 @@
     </row>
     <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>37</v>
@@ -6328,7 +6326,7 @@
     </row>
     <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>37</v>
@@ -6445,7 +6443,7 @@
     </row>
     <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>37</v>
@@ -6530,7 +6528,7 @@
         <v>25</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AH37" s="1">
         <f t="shared" si="6"/>
@@ -6556,7 +6554,7 @@
     </row>
     <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
@@ -6667,7 +6665,7 @@
     </row>
     <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>37</v>
@@ -6776,7 +6774,7 @@
     </row>
     <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>35</v>
@@ -6859,7 +6857,7 @@
         <v>3.3424</v>
       </c>
       <c r="AG40" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH40" s="1">
         <f t="shared" si="6"/>
@@ -6885,7 +6883,7 @@
     </row>
     <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -6968,7 +6966,7 @@
         <v>3.92</v>
       </c>
       <c r="AG41" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH41" s="1">
         <f t="shared" si="6"/>
@@ -6994,7 +6992,7 @@
     </row>
     <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>35</v>
@@ -7103,7 +7101,7 @@
     </row>
     <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>35</v>
@@ -7186,7 +7184,7 @@
         <v>2.2627999999999999</v>
       </c>
       <c r="AG43" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH43" s="1">
         <f t="shared" si="6"/>
@@ -7212,7 +7210,7 @@
     </row>
     <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>37</v>
@@ -7297,7 +7295,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="AG44" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH44" s="1">
         <f t="shared" si="6"/>
@@ -7323,7 +7321,7 @@
     </row>
     <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>37</v>
@@ -7432,7 +7430,7 @@
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>37</v>
@@ -7549,7 +7547,7 @@
     </row>
     <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>37</v>
@@ -7664,7 +7662,7 @@
     </row>
     <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
@@ -7777,7 +7775,7 @@
     </row>
     <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>37</v>
@@ -7799,10 +7797,10 @@
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="K49" s="9">
         <v>78</v>
@@ -7888,7 +7886,7 @@
     </row>
     <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>37</v>
@@ -8001,7 +7999,7 @@
     </row>
     <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>35</v>
@@ -8086,7 +8084,7 @@
         <v>8.6932000000000009</v>
       </c>
       <c r="AG51" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH51" s="1">
         <f t="shared" si="6"/>
@@ -31928,7 +31926,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2">
         <v>24</v>
@@ -31936,7 +31934,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>16</v>
@@ -31944,7 +31942,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>204</v>
@@ -31952,7 +31950,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>48</v>
@@ -31960,7 +31958,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>16</v>
@@ -31968,7 +31966,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>1000</v>
@@ -31976,7 +31974,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>1500</v>
@@ -31984,7 +31982,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>28</v>
@@ -31992,7 +31990,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10">
         <v>200</v>
@@ -32000,7 +31998,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -32008,7 +32006,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -32016,7 +32014,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13">
         <v>48</v>
@@ -32024,7 +32022,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14">
         <v>130</v>
@@ -32032,7 +32030,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15">
         <v>15</v>
@@ -32040,7 +32038,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16">
         <v>170</v>
